--- a/public/downloads/LeeEpitaxial2020.xlsx
+++ b/public/downloads/LeeEpitaxial2020.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,10 +169,31 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>OOH</t>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>OH</t>
+  </si>
+  <si>
+    <t>OOH</t>
   </si>
   <si>
     <t>O</t>
@@ -659,10 +682,10 @@
         <v>23</v>
       </c>
       <c r="N3" s="5">
-        <v>142.5086839199066</v>
+        <v>142508.6839199066</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03159837780929194</v>
+        <v>31.59837780929194</v>
       </c>
       <c r="P3" s="5">
         <v>4510</v>
@@ -709,10 +732,10 @@
         <v>23</v>
       </c>
       <c r="N4" s="5">
-        <v>209.1713175773621</v>
+        <v>209171.3175773621</v>
       </c>
       <c r="O4" s="4">
-        <v>0.05479992600926436</v>
+        <v>54.79992600926436</v>
       </c>
       <c r="P4" s="5">
         <v>3817</v>
@@ -759,10 +782,10 @@
         <v>23</v>
       </c>
       <c r="N5" s="5">
-        <v>483.4279458522797</v>
+        <v>483427.9458522797</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1542526949113847</v>
+        <v>154.2526949113847</v>
       </c>
       <c r="P5" s="5">
         <v>3134</v>
@@ -809,10 +832,10 @@
         <v>23</v>
       </c>
       <c r="N6" s="5">
-        <v>356.1832466125488</v>
+        <v>356183.2466125488</v>
       </c>
       <c r="O6" s="4">
-        <v>0.1003050539601658</v>
+        <v>100.3050539601658</v>
       </c>
       <c r="P6" s="5">
         <v>3551</v>
@@ -859,10 +882,10 @@
         <v>23</v>
       </c>
       <c r="N7" s="5">
-        <v>496.8613429069519</v>
+        <v>496861.3429069519</v>
       </c>
       <c r="O7" s="4">
-        <v>0.2401456466442493</v>
+        <v>240.1456466442493</v>
       </c>
       <c r="P7" s="5">
         <v>2069</v>
@@ -909,10 +932,10 @@
         <v>23</v>
       </c>
       <c r="N8" s="5">
-        <v>50.38365697860718</v>
+        <v>50383.65697860718</v>
       </c>
       <c r="O8" s="4">
-        <v>0.0159039321270856</v>
+        <v>15.9039321270856</v>
       </c>
       <c r="P8" s="5">
         <v>3168</v>
@@ -959,10 +982,10 @@
         <v>23</v>
       </c>
       <c r="N9" s="5">
-        <v>130.2849428653717</v>
+        <v>130284.9428653717</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03350088528294464</v>
+        <v>33.50088528294464</v>
       </c>
       <c r="P9" s="5">
         <v>3889</v>
@@ -1009,10 +1032,10 @@
         <v>23</v>
       </c>
       <c r="N10" s="5">
-        <v>232.5327050685883</v>
+        <v>232532.7050685883</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08660435942964181</v>
+        <v>86.60435942964182</v>
       </c>
       <c r="P10" s="5">
         <v>2685</v>
@@ -1059,10 +1082,10 @@
         <v>23</v>
       </c>
       <c r="N11" s="5">
-        <v>129.407369852066</v>
+        <v>129407.369852066</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04130461852922632</v>
+        <v>41.30461852922632</v>
       </c>
       <c r="P11" s="5">
         <v>3133</v>
@@ -1109,10 +1132,10 @@
         <v>23</v>
       </c>
       <c r="N12" s="5">
-        <v>52.01526665687561</v>
+        <v>52015.26665687561</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02039814378701004</v>
+        <v>20.39814378701005</v>
       </c>
       <c r="P12" s="5">
         <v>2550</v>
@@ -1159,10 +1182,10 @@
         <v>23</v>
       </c>
       <c r="N13" s="5">
-        <v>243.8379006385803</v>
+        <v>243837.9006385803</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07329062237408486</v>
+        <v>73.29062237408486</v>
       </c>
       <c r="P13" s="5">
         <v>3327</v>
@@ -1209,10 +1232,10 @@
         <v>23</v>
       </c>
       <c r="N14" s="5">
-        <v>1009.138634681702</v>
+        <v>1009138.634681702</v>
       </c>
       <c r="O14" s="4">
-        <v>0.3333791326996041</v>
+        <v>333.3791326996041</v>
       </c>
       <c r="P14" s="5">
         <v>3027</v>
@@ -1259,10 +1282,10 @@
         <v>23</v>
       </c>
       <c r="N15" s="5">
-        <v>613.6482055187225</v>
+        <v>613648.2055187225</v>
       </c>
       <c r="O15" s="4">
-        <v>0.3424376146867871</v>
+        <v>342.4376146867871</v>
       </c>
       <c r="P15" s="5">
         <v>1792</v>
@@ -1309,10 +1332,10 @@
         <v>23</v>
       </c>
       <c r="N16" s="5">
-        <v>354.4138407707214</v>
+        <v>354413.8407707214</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09831174501268278</v>
+        <v>98.31174501268278</v>
       </c>
       <c r="P16" s="5">
         <v>3605</v>
@@ -1359,10 +1382,10 @@
         <v>23</v>
       </c>
       <c r="N17" s="5">
-        <v>230.2374286651611</v>
+        <v>230237.4286651611</v>
       </c>
       <c r="O17" s="4">
-        <v>0.09928306540110442</v>
+        <v>99.28306540110442</v>
       </c>
       <c r="P17" s="5">
         <v>2319</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,34 +1497,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1911446823640812</v>
+        <v>0.1133061217779714</v>
       </c>
       <c r="C3" s="4">
-        <v>0.09935605155331946</v>
+        <v>0.1133061217779714</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1449047687086775</v>
+        <v>0.1124558214202782</v>
       </c>
       <c r="E3" s="4">
-        <v>90.29336734693881</v>
+        <v>91.27551020408163</v>
       </c>
       <c r="F3" s="4">
-        <v>84.08976510067114</v>
+        <v>89.23238255033557</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -1501,34 +1556,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1133061217779714</v>
+      </c>
+      <c r="O3" s="5">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.08884565751940166</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08884565751940166</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.06653572274080144</v>
+        <v>0.2210586321204127</v>
       </c>
       <c r="C4" s="4">
-        <v>0.06653572274080144</v>
+        <v>0.277614569047261</v>
       </c>
       <c r="D4" s="4">
-        <v>0.08504613493769853</v>
+        <v>0.3718663839676637</v>
       </c>
       <c r="E4" s="4">
-        <v>92.35969387755102</v>
+        <v>85.57397959183673</v>
       </c>
       <c r="F4" s="4">
-        <v>89.8741610738255</v>
+        <v>68.29697986577182</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -1542,25 +1615,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.277614569047261</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1655839161310514</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1744447667267249</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1289292508773122</v>
+        <v>0.09652670285565586</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1289292508773122</v>
+        <v>0.09652670285565586</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1452947276759242</v>
+        <v>0.09756500522856067</v>
       </c>
       <c r="E5" s="4">
-        <v>93.39650145772593</v>
+        <v>92.52186588921282</v>
       </c>
       <c r="F5" s="4">
-        <v>93.92617449664429</v>
+        <v>93.17833173537873</v>
       </c>
       <c r="G5" s="5">
         <v>7</v>
@@ -1583,9 +1674,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.09014831679262818</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.0879551491263659</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.0879551491263659</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1705,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1724,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1766,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,132 +1797,202 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2564484900378403</v>
+        <v>0.5640655586395233</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3890513716235375</v>
+        <v>0.6545561948439484</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2466321910516385</v>
+        <v>0.5334202985279823</v>
       </c>
       <c r="E3" s="4">
-        <v>85.23384353741496</v>
+        <v>83.35884353741496</v>
       </c>
       <c r="F3" s="4">
-        <v>68.79194630872483</v>
+        <v>79.88394854586129</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
+        <v>6</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
         <v>2</v>
       </c>
-      <c r="I3" s="5">
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>2</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.6545561948439484</v>
+      </c>
+      <c r="O3" s="5">
         <v>6</v>
       </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="P3" s="4">
+        <v>0.1875474920198457</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1294091410872274</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1419359731494048</v>
+        <v>0.7164587818487576</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1338694472879354</v>
+        <v>0.9775003003887974</v>
       </c>
       <c r="D4" s="4">
-        <v>0.189098494177852</v>
+        <v>0.7760624729498318</v>
       </c>
       <c r="E4" s="4">
-        <v>90.14030612244898</v>
+        <v>79.93622448979592</v>
       </c>
       <c r="F4" s="4">
-        <v>84.42673378076063</v>
+        <v>69.04082774049216</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.7164587818487576</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.9775003003887974</v>
+      </c>
+      <c r="R4" s="5">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2180606595016051</v>
+        <v>0.9567131164451439</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2180606595016051</v>
+        <v>1.075180016346928</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2302679632299812</v>
+        <v>0.9084772231956322</v>
       </c>
       <c r="E5" s="4">
-        <v>92.4198250728863</v>
+        <v>83.97473275024298</v>
       </c>
       <c r="F5" s="4">
-        <v>91.76414189837004</v>
+        <v>83.9181847235543</v>
       </c>
       <c r="G5" s="5">
         <v>7</v>
       </c>
       <c r="H5" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>1.075180016346928</v>
+      </c>
+      <c r="O5" s="5">
+        <v>5</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1980335990133864</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1113933787562428</v>
+      </c>
+      <c r="R5" s="5">
+        <v>5</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2003,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2011,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2022,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2064,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,34 +2095,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2194976354229681</v>
+        <v>0.06653572274080144</v>
       </c>
       <c r="C3" s="4">
-        <v>0.08948606117675695</v>
+        <v>0.06653572274080144</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1427826428997747</v>
+        <v>0.08504613493769853</v>
       </c>
       <c r="E3" s="4">
-        <v>91.87925170068027</v>
+        <v>92.35969387755102</v>
       </c>
       <c r="F3" s="4">
-        <v>84.56655480984337</v>
+        <v>89.8741610738255</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -1927,34 +2154,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.02296198970657626</v>
+      </c>
+      <c r="O3" s="5">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06981223397788872</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06981223397788872</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.09451137892578387</v>
+        <v>0.1911446823640812</v>
       </c>
       <c r="C4" s="4">
-        <v>0.09451137892578387</v>
+        <v>0.09935605155331946</v>
       </c>
       <c r="D4" s="4">
-        <v>0.09945331923340106</v>
+        <v>0.1449047687086775</v>
       </c>
       <c r="E4" s="4">
-        <v>93.12925170068026</v>
+        <v>90.29336734693881</v>
       </c>
       <c r="F4" s="4">
-        <v>87.83137583892614</v>
+        <v>84.08976510067114</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -1968,25 +2213,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.05394071196694365</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.196863689653776</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.08900115728393132</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1333799419702148</v>
+        <v>0.1289292508773122</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1333799419702148</v>
+        <v>0.1289292508773122</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1336885237311662</v>
+        <v>0.1452947276759242</v>
       </c>
       <c r="E5" s="4">
-        <v>94.21768707482993</v>
+        <v>93.39650145772593</v>
       </c>
       <c r="F5" s="4">
-        <v>92.91626717801215</v>
+        <v>93.92617449664429</v>
       </c>
       <c r="G5" s="5">
         <v>7</v>
@@ -2009,9 +2272,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.009238960732738428</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1276093993440639</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1276093993440639</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2303,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2311,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2322,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2364,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,34 +2395,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2175200141564915</v>
+        <v>0.1419359731494048</v>
       </c>
       <c r="C3" s="4">
-        <v>0.09216840204589971</v>
+        <v>0.1338694472879354</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1319706583607427</v>
+        <v>0.189098494177852</v>
       </c>
       <c r="E3" s="4">
-        <v>87.55952380952382</v>
+        <v>90.14030612244898</v>
       </c>
       <c r="F3" s="4">
-        <v>77.5908836689037</v>
+        <v>84.42673378076063</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2140,34 +2454,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.04971069208705054</v>
+      </c>
+      <c r="O3" s="5">
+        <v>7</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1419359731494048</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1267679198469281</v>
+      </c>
+      <c r="R3" s="5">
+        <v>7</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1541559844375548</v>
+        <v>0.2564484900378403</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1471297490562173</v>
+        <v>0.3890513716235375</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1370707302452026</v>
+        <v>0.2466321910516385</v>
       </c>
       <c r="E4" s="4">
-        <v>88.76700680272108</v>
+        <v>85.23384353741496</v>
       </c>
       <c r="F4" s="4">
-        <v>80.04893736017897</v>
+        <v>68.79194630872483</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -2181,25 +2513,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2564484900378403</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3890513716235375</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.08408288683278897</v>
+        <v>0.2180606595016051</v>
       </c>
       <c r="C5" s="4">
-        <v>0.08408288683278897</v>
+        <v>0.2180606595016051</v>
       </c>
       <c r="D5" s="4">
-        <v>0.08411714505945968</v>
+        <v>0.2302679632299812</v>
       </c>
       <c r="E5" s="4">
-        <v>91.64723032069971</v>
+        <v>92.4198250728863</v>
       </c>
       <c r="F5" s="4">
-        <v>91.69702780441035</v>
+        <v>91.76414189837004</v>
       </c>
       <c r="G5" s="5">
         <v>7</v>
@@ -2222,9 +2570,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1045510958980945</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1848499415991613</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1848499415991613</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2601,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2609,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2620,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2662,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,34 +2693,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3846001003339552</v>
+        <v>0.09451137892578387</v>
       </c>
       <c r="C3" s="4">
-        <v>0.414034962318495</v>
+        <v>0.09451137892578387</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4293613855197336</v>
+        <v>0.09945331923340106</v>
       </c>
       <c r="E3" s="4">
-        <v>80.52295918367346</v>
+        <v>93.12925170068026</v>
       </c>
       <c r="F3" s="4">
-        <v>83.25782997762863</v>
+        <v>87.83137583892614</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2353,34 +2752,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.009904043945315522</v>
+      </c>
+      <c r="O3" s="5">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.09451137892578387</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09451137892578387</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.297071475339413</v>
+        <v>0.2194976354229681</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3116706846044168</v>
+        <v>0.08948606117675695</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3030707759682532</v>
+        <v>0.1427826428997747</v>
       </c>
       <c r="E4" s="4">
-        <v>81.203231292517</v>
+        <v>91.87925170068027</v>
       </c>
       <c r="F4" s="4">
-        <v>82.83557046979867</v>
+        <v>84.56655480984337</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -2394,25 +2811,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.06429992150146784</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2059839314013701</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09290109631511555</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3970233860392121</v>
+        <v>0.1333799419702148</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3970233860392121</v>
+        <v>0.1333799419702148</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4009608177834844</v>
+        <v>0.1336885237311662</v>
       </c>
       <c r="E5" s="4">
-        <v>80.96209912536443</v>
+        <v>94.21768707482993</v>
       </c>
       <c r="F5" s="4">
-        <v>86.59635666347076</v>
+        <v>92.91626717801215</v>
       </c>
       <c r="G5" s="5">
         <v>7</v>
@@ -2435,9 +2870,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.09128848341902085</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.09438151545917403</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.09438151545917403</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2901,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2909,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2920,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2962,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,34 +2993,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6295950047269407</v>
+        <v>0.1541559844375548</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4960441890446035</v>
+        <v>0.1471297490562173</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5210476375715878</v>
+        <v>0.1370707302452026</v>
       </c>
       <c r="E3" s="4">
-        <v>95.21683673469387</v>
+        <v>88.76700680272108</v>
       </c>
       <c r="F3" s="4">
-        <v>88.65072706935122</v>
+        <v>80.04893736017897</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2566,34 +3052,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1397295112876731</v>
+      </c>
+      <c r="O3" s="5">
+        <v>7</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06128644960453299</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06095449657385991</v>
+      </c>
+      <c r="R3" s="5">
+        <v>7</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3888844085958088</v>
+        <v>0.2175200141564915</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3724018482197771</v>
+        <v>0.09216840204589971</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3672246804560562</v>
+        <v>0.1319706583607427</v>
       </c>
       <c r="E4" s="4">
-        <v>96.16071428571429</v>
+        <v>87.55952380952382</v>
       </c>
       <c r="F4" s="4">
-        <v>91.85123042505592</v>
+        <v>77.5908836689037</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -2607,25 +3111,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.09216840204589971</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1789434498339872</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.07185559852540564</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2177593262499791</v>
+        <v>0.08408288683278897</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2177593262499791</v>
+        <v>0.08408288683278897</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2182400802847698</v>
+        <v>0.08411714505945968</v>
       </c>
       <c r="E5" s="4">
-        <v>97.87172011661808</v>
+        <v>91.64723032069971</v>
       </c>
       <c r="F5" s="4">
-        <v>97.81399808245448</v>
+        <v>91.69702780441035</v>
       </c>
       <c r="G5" s="5">
         <v>7</v>
@@ -2648,9 +3170,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.04044401843576192</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.06778286653379419</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.06778286653379419</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3201,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3209,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3220,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3262,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,132 +3293,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.623430916461837</v>
+        <v>0.297071475339413</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6563968782722824</v>
+        <v>0.3116706846044168</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7375291429861832</v>
+        <v>0.3030707759682532</v>
       </c>
       <c r="E3" s="4">
-        <v>75.16581632653062</v>
+        <v>81.203231292517</v>
       </c>
       <c r="F3" s="4">
-        <v>74.35822147651007</v>
+        <v>82.83557046979867</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.3116706846044168</v>
+      </c>
+      <c r="O3" s="5">
+        <v>7</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1019887068809164</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09987371156104298</v>
+      </c>
+      <c r="R3" s="5">
+        <v>7</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6138662377272102</v>
+        <v>0.3846001003339552</v>
       </c>
       <c r="C4" s="4">
-        <v>0.583208133809886</v>
+        <v>0.414034962318495</v>
       </c>
       <c r="D4" s="4">
-        <v>0.6171529421481541</v>
+        <v>0.4293613855197336</v>
       </c>
       <c r="E4" s="4">
-        <v>76.03316326530613</v>
+        <v>80.52295918367346</v>
       </c>
       <c r="F4" s="4">
-        <v>78.22147651006712</v>
+        <v>83.25782997762863</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.414034962318495</v>
+      </c>
+      <c r="O4" s="5">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1366838403186976</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1225702609533232</v>
+      </c>
+      <c r="R4" s="5">
+        <v>7</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5604285362144122</v>
+        <v>0.3970233860392121</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5959811757201816</v>
+        <v>0.3970233860392121</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5774503242324539</v>
+        <v>0.4009608177834844</v>
       </c>
       <c r="E5" s="4">
-        <v>75.88921282798837</v>
+        <v>80.96209912536443</v>
       </c>
       <c r="F5" s="4">
-        <v>79.09395973154358</v>
+        <v>86.59635666347076</v>
       </c>
       <c r="G5" s="5">
         <v>7</v>
       </c>
       <c r="H5" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.3970233860392121</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.08816369487721383</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.08816369487721383</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3501,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3509,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3520,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3562,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,34 +3593,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4004468515112301</v>
+        <v>0.3888844085958088</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2406614878749153</v>
+        <v>0.3724018482197771</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2739081538814077</v>
+        <v>0.3672246804560562</v>
       </c>
       <c r="E3" s="4">
-        <v>92.98469387755102</v>
+        <v>96.16071428571429</v>
       </c>
       <c r="F3" s="4">
-        <v>85.55928411633116</v>
+        <v>91.85123042505592</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2992,34 +3652,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3724018482197771</v>
+      </c>
+      <c r="O3" s="5">
+        <v>7</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06231252140973265</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05237709832422967</v>
+      </c>
+      <c r="R3" s="5">
+        <v>7</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2437350696052203</v>
+        <v>0.6295950047269407</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2437350696052203</v>
+        <v>0.4960441890446035</v>
       </c>
       <c r="D4" s="4">
-        <v>0.24299253729267</v>
+        <v>0.5210476375715878</v>
       </c>
       <c r="E4" s="4">
-        <v>95.31887755102041</v>
+        <v>95.21683673469387</v>
       </c>
       <c r="F4" s="4">
-        <v>93.74580536912751</v>
+        <v>88.65072706935122</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -3033,25 +3711,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.4960441890446035</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.163136264403132</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.03944726496105962</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1804262635331309</v>
+        <v>0.2177593262499791</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1804262635331309</v>
+        <v>0.2177593262499791</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1851139219110977</v>
+        <v>0.2182400802847698</v>
       </c>
       <c r="E5" s="4">
-        <v>96.90962099125363</v>
+        <v>97.87172011661808</v>
       </c>
       <c r="F5" s="4">
-        <v>96.58197507190796</v>
+        <v>97.81399808245448</v>
       </c>
       <c r="G5" s="5">
         <v>7</v>
@@ -3074,9 +3770,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.2177593262499791</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.03709456610906362</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.03709456610906362</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3801,1466 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.6138662377272102</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.583208133809886</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.6171529421481541</v>
+      </c>
+      <c r="E3" s="4">
+        <v>76.03316326530613</v>
+      </c>
+      <c r="F3" s="4">
+        <v>78.22147651006712</v>
+      </c>
+      <c r="G3" s="5">
+        <v>8</v>
+      </c>
+      <c r="H3" s="5">
+        <v>5</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>3</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>3</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.583208133809886</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1477209723504735</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08681526454016449</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.623430916461837</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.6563968782722824</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.7375291429861832</v>
+      </c>
+      <c r="E4" s="4">
+        <v>75.16581632653062</v>
+      </c>
+      <c r="F4" s="4">
+        <v>74.35822147651007</v>
+      </c>
+      <c r="G4" s="5">
+        <v>8</v>
+      </c>
+      <c r="H4" s="5">
+        <v>4</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.623430916461837</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6563968782722824</v>
+      </c>
+      <c r="R4" s="5">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.5604285362144122</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.5959811757201816</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.5774503242324539</v>
+      </c>
+      <c r="E5" s="4">
+        <v>75.88921282798837</v>
+      </c>
+      <c r="F5" s="4">
+        <v>79.09395973154358</v>
+      </c>
+      <c r="G5" s="5">
+        <v>7</v>
+      </c>
+      <c r="H5" s="5">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>3</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5604285362144122</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.5959811757201816</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.2437350696052203</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2437350696052203</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.24299253729267</v>
+      </c>
+      <c r="E3" s="4">
+        <v>95.31887755102041</v>
+      </c>
+      <c r="F3" s="4">
+        <v>93.74580536912751</v>
+      </c>
+      <c r="G3" s="5">
+        <v>8</v>
+      </c>
+      <c r="H3" s="5">
+        <v>8</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.2437350696052203</v>
+      </c>
+      <c r="O3" s="5">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.05356362553168736</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05356362553168736</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4004468515112301</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2406614878749153</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2739081538814077</v>
+      </c>
+      <c r="E4" s="4">
+        <v>92.98469387755102</v>
+      </c>
+      <c r="F4" s="4">
+        <v>85.55928411633116</v>
+      </c>
+      <c r="G4" s="5">
+        <v>8</v>
+      </c>
+      <c r="H4" s="5">
+        <v>5</v>
+      </c>
+      <c r="I4" s="5">
+        <v>3</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.2406614878749153</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1846815729295457</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.03983393486916952</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.1804262635331309</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.1804262635331309</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.1851139219110977</v>
+      </c>
+      <c r="E5" s="4">
+        <v>96.90962099125363</v>
+      </c>
+      <c r="F5" s="4">
+        <v>96.58197507190796</v>
+      </c>
+      <c r="G5" s="5">
+        <v>7</v>
+      </c>
+      <c r="H5" s="5">
+        <v>7</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.1804262635331309</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.02919788030050202</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.02919788030050202</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>47.82608695652174</v>
+      </c>
+      <c r="C3" s="3">
+        <v>13.04347826086956</v>
+      </c>
+      <c r="D3" s="3">
+        <v>39.1304347826087</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>39.1304347826087</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.2782893856979233</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.3334572792215159</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.3345364956501036</v>
+      </c>
+      <c r="K3" s="4">
+        <v>75.73794735285416</v>
+      </c>
+      <c r="L3" s="4">
+        <v>75.36620951269508</v>
+      </c>
+      <c r="M3" s="5">
+        <v>23</v>
+      </c>
+      <c r="N3" s="5">
+        <v>142508.6839199066</v>
+      </c>
+      <c r="O3" s="4">
+        <v>31.59837780929194</v>
+      </c>
+      <c r="P3" s="5">
+        <v>4510</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>56.52173913043478</v>
+      </c>
+      <c r="C4" s="3">
+        <v>30.43478260869566</v>
+      </c>
+      <c r="D4" s="3">
+        <v>13.04347826086956</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>13.04347826086956</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1.320910894461595</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.1157647580773866</v>
+      </c>
+      <c r="J4" s="4">
+        <v>1.459403975386669</v>
+      </c>
+      <c r="K4" s="4">
+        <v>83.17805383022774</v>
+      </c>
+      <c r="L4" s="4">
+        <v>79.85069545764105</v>
+      </c>
+      <c r="M4" s="5">
+        <v>23</v>
+      </c>
+      <c r="N4" s="5">
+        <v>209171.3175773621</v>
+      </c>
+      <c r="O4" s="4">
+        <v>54.79992600926436</v>
+      </c>
+      <c r="P4" s="5">
+        <v>3817</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>91.30434782608695</v>
+      </c>
+      <c r="C5" s="3">
+        <v>8.695652173913043</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.07308133749450024</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.0619889892310682</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.09028343932449844</v>
+      </c>
+      <c r="K5" s="4">
+        <v>86.40343093759242</v>
+      </c>
+      <c r="L5" s="4">
+        <v>86.35200855947809</v>
+      </c>
+      <c r="M5" s="5">
+        <v>23</v>
+      </c>
+      <c r="N5" s="5">
+        <v>483427.9458522797</v>
+      </c>
+      <c r="O5" s="4">
+        <v>154.2526949113847</v>
+      </c>
+      <c r="P5" s="5">
+        <v>3134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>78.26086956521739</v>
+      </c>
+      <c r="C6" s="3">
+        <v>21.73913043478261</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.1287799601170593</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.1473242480908775</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.1403086136101213</v>
+      </c>
+      <c r="K6" s="4">
+        <v>84.42324755989354</v>
+      </c>
+      <c r="L6" s="4">
+        <v>83.44081315047387</v>
+      </c>
+      <c r="M6" s="5">
+        <v>23</v>
+      </c>
+      <c r="N6" s="5">
+        <v>356183.2466125488</v>
+      </c>
+      <c r="O6" s="4">
+        <v>100.3050539601658</v>
+      </c>
+      <c r="P6" s="5">
+        <v>3551</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>86.95652173913044</v>
+      </c>
+      <c r="C7" s="3">
+        <v>13.04347826086956</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.08343477587082107</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.04643900537879067</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.05415745624514322</v>
+      </c>
+      <c r="K7" s="4">
+        <v>95.10795622596865</v>
+      </c>
+      <c r="L7" s="4">
+        <v>93.07363096975018</v>
+      </c>
+      <c r="M7" s="5">
+        <v>23</v>
+      </c>
+      <c r="N7" s="5">
+        <v>496861.3429069519</v>
+      </c>
+      <c r="O7" s="4">
+        <v>240.1456466442493</v>
+      </c>
+      <c r="P7" s="5">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>86.95652173913044</v>
+      </c>
+      <c r="C8" s="3">
+        <v>13.04347826086956</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.1152662014386168</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.10993375688367</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.1146092535360559</v>
+      </c>
+      <c r="K8" s="4">
+        <v>89.67169476486248</v>
+      </c>
+      <c r="L8" s="4">
+        <v>83.15144441202335</v>
+      </c>
+      <c r="M8" s="5">
+        <v>23</v>
+      </c>
+      <c r="N8" s="5">
+        <v>50383.65697860718</v>
+      </c>
+      <c r="O8" s="4">
+        <v>15.9039321270856</v>
+      </c>
+      <c r="P8" s="5">
+        <v>3168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>65.21739130434783</v>
+      </c>
+      <c r="C9" s="3">
+        <v>8.695652173913043</v>
+      </c>
+      <c r="D9" s="3">
+        <v>26.08695652173913</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>26.08695652173913</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.3747080601757622</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.3495615294573178</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.4266194208994908</v>
+      </c>
+      <c r="K9" s="4">
+        <v>82.35581188997338</v>
+      </c>
+      <c r="L9" s="4">
+        <v>77.34023927633655</v>
+      </c>
+      <c r="M9" s="5">
+        <v>23</v>
+      </c>
+      <c r="N9" s="5">
+        <v>130284.9428653717</v>
+      </c>
+      <c r="O9" s="4">
+        <v>33.50088528294464</v>
+      </c>
+      <c r="P9" s="5">
+        <v>3889</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>91.30434782608695</v>
+      </c>
+      <c r="C10" s="3">
+        <v>8.695652173913043</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.1315944862809463</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.09456050528262595</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1225857052938357</v>
+      </c>
+      <c r="K10" s="4">
+        <v>91.95652173913047</v>
+      </c>
+      <c r="L10" s="4">
+        <v>89.0954187335882</v>
+      </c>
+      <c r="M10" s="5">
+        <v>23</v>
+      </c>
+      <c r="N10" s="5">
+        <v>232532.7050685883</v>
+      </c>
+      <c r="O10" s="4">
+        <v>86.60435942964182</v>
+      </c>
+      <c r="P10" s="5">
+        <v>2685</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>69.56521739130434</v>
+      </c>
+      <c r="C11" s="3">
+        <v>30.43478260869566</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.1948271868126995</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.1849642358356063</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.2058733502194809</v>
+      </c>
+      <c r="K11" s="4">
+        <v>89.12747707778766</v>
+      </c>
+      <c r="L11" s="4">
+        <v>81.22167104367171</v>
+      </c>
+      <c r="M11" s="5">
+        <v>23</v>
+      </c>
+      <c r="N11" s="5">
+        <v>129407.369852066</v>
+      </c>
+      <c r="O11" s="4">
+        <v>41.30461852922632</v>
+      </c>
+      <c r="P11" s="5">
+        <v>3133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>91.30434782608695</v>
+      </c>
+      <c r="C12" s="3">
+        <v>8.695652173913043</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.1332449169926717</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.09400801035767536</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.107270426953808</v>
+      </c>
+      <c r="K12" s="4">
+        <v>93.02573203194322</v>
+      </c>
+      <c r="L12" s="4">
+        <v>88.24336154070579</v>
+      </c>
+      <c r="M12" s="5">
+        <v>23</v>
+      </c>
+      <c r="N12" s="5">
+        <v>52015.26665687561</v>
+      </c>
+      <c r="O12" s="4">
+        <v>20.39814378701005</v>
+      </c>
+      <c r="P12" s="5">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>82.60869565217391</v>
+      </c>
+      <c r="C13" s="3">
+        <v>17.39130434782609</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.1041877939671618</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.0663389228621372</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.08255883270578172</v>
+      </c>
+      <c r="K13" s="4">
+        <v>89.22360248447202</v>
+      </c>
+      <c r="L13" s="4">
+        <v>82.73903316797995</v>
+      </c>
+      <c r="M13" s="5">
+        <v>23</v>
+      </c>
+      <c r="N13" s="5">
+        <v>243837.9006385803</v>
+      </c>
+      <c r="O13" s="4">
+        <v>73.29062237408486</v>
+      </c>
+      <c r="P13" s="5">
+        <v>3327</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>91.30434782608695</v>
+      </c>
+      <c r="C14" s="3">
+        <v>8.695652173913043</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.1098489670320612</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.1035358891305267</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.08599419481454855</v>
+      </c>
+      <c r="K14" s="4">
+        <v>80.89322685595977</v>
+      </c>
+      <c r="L14" s="4">
+        <v>84.12703044450961</v>
+      </c>
+      <c r="M14" s="5">
+        <v>23</v>
+      </c>
+      <c r="N14" s="5">
+        <v>1009138.634681702</v>
+      </c>
+      <c r="O14" s="4">
+        <v>333.3791326996041</v>
+      </c>
+      <c r="P14" s="5">
+        <v>3027</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>86.95652173913044</v>
+      </c>
+      <c r="C15" s="3">
+        <v>13.04347826086956</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.08970661953332011</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.04314926203997053</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.05268319714153057</v>
+      </c>
+      <c r="K15" s="4">
+        <v>96.35314995563444</v>
+      </c>
+      <c r="L15" s="4">
+        <v>92.55276724053935</v>
+      </c>
+      <c r="M15" s="5">
+        <v>23</v>
+      </c>
+      <c r="N15" s="5">
+        <v>613648.2055187225</v>
+      </c>
+      <c r="O15" s="4">
+        <v>342.4376146867871</v>
+      </c>
+      <c r="P15" s="5">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>56.52173913043478</v>
+      </c>
+      <c r="C16" s="3">
+        <v>8.695652173913043</v>
+      </c>
+      <c r="D16" s="3">
+        <v>34.78260869565217</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>34.78260869565217</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.4387919506086683</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.4187375798977445</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.4724892259282846</v>
+      </c>
+      <c r="K16" s="4">
+        <v>75.68766637089621</v>
+      </c>
+      <c r="L16" s="4">
+        <v>77.14327400058339</v>
+      </c>
+      <c r="M16" s="5">
+        <v>23</v>
+      </c>
+      <c r="N16" s="5">
+        <v>354413.8407707214</v>
+      </c>
+      <c r="O16" s="4">
+        <v>98.31174501268278</v>
+      </c>
+      <c r="P16" s="5">
+        <v>3605</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>86.95652173913044</v>
+      </c>
+      <c r="C17" s="3">
+        <v>13.04347826086956</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.09175420651275559</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.04160319203514303</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.05198712800386202</v>
+      </c>
+      <c r="K17" s="4">
+        <v>94.99112688553681</v>
+      </c>
+      <c r="L17" s="4">
+        <v>91.76150179943625</v>
+      </c>
+      <c r="M17" s="5">
+        <v>23</v>
+      </c>
+      <c r="N17" s="5">
+        <v>230237.4286651611</v>
+      </c>
+      <c r="O17" s="4">
+        <v>99.28306540110442</v>
+      </c>
+      <c r="P17" s="5">
+        <v>2319</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3847,9 +6015,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>11</v>
+      </c>
+      <c r="C3" s="5">
+        <v>3</v>
+      </c>
+      <c r="D3" s="5">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>9</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>6</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>13</v>
+      </c>
+      <c r="C4" s="5">
+        <v>7</v>
+      </c>
+      <c r="D4" s="5">
+        <v>3</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>3</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>21</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>18</v>
+      </c>
+      <c r="C6" s="5">
+        <v>5</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>20</v>
+      </c>
+      <c r="C7" s="5">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>20</v>
+      </c>
+      <c r="C8" s="5">
+        <v>3</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>15</v>
+      </c>
+      <c r="C9" s="5">
+        <v>2</v>
+      </c>
+      <c r="D9" s="5">
+        <v>6</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>6</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>21</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>16</v>
+      </c>
+      <c r="C11" s="5">
+        <v>7</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>21</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>19</v>
+      </c>
+      <c r="C13" s="5">
+        <v>4</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>21</v>
+      </c>
+      <c r="C14" s="5">
+        <v>2</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>20</v>
+      </c>
+      <c r="C15" s="5">
+        <v>3</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>13</v>
+      </c>
+      <c r="C16" s="5">
+        <v>2</v>
+      </c>
+      <c r="D16" s="5">
+        <v>8</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>8</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>3</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>20</v>
+      </c>
+      <c r="C17" s="5">
+        <v>3</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6783,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6825,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,34 +6856,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3454280818597439</v>
+        <v>0.1932259966192582</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5833927666654404</v>
+        <v>0.1579771080236654</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4678601945535306</v>
+        <v>0.2281029392538407</v>
       </c>
       <c r="E3" s="4">
-        <v>73.23554421768702</v>
+        <v>76.83248299319729</v>
       </c>
       <c r="F3" s="4">
-        <v>67.48042505592848</v>
+        <v>77.74888143176734</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>3</v>
@@ -3960,34 +6915,50 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>4</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1932259966192582</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1579771080236654</v>
+      </c>
+      <c r="R3" s="5">
+        <v>4</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1932259966192582</v>
+        <v>0.3454280818597439</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1579771080236654</v>
+        <v>0.5833927666654404</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2281029392538407</v>
+        <v>0.4678601945535306</v>
       </c>
       <c r="E4" s="4">
-        <v>76.83248299319729</v>
+        <v>73.23554421768702</v>
       </c>
       <c r="F4" s="4">
-        <v>77.74888143176734</v>
+        <v>67.48042505592848</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
         <v>3</v>
@@ -4001,10 +6972,26 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3454280818597439</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5833927666654404</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.29877474903146</v>
@@ -4042,9 +7029,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.29877474903146</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3214858348364231</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7058,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7077,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7119,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,37 +7150,55 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>3.522415383945315</v>
+        <v>0.3796898464672829</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.4173315412662693</v>
       </c>
       <c r="D3" s="4">
-        <v>3.853739961276858</v>
+        <v>0.3610559870062211</v>
       </c>
       <c r="E3" s="4">
-        <v>80.13605442176872</v>
+        <v>83.54591836734694</v>
       </c>
       <c r="F3" s="4">
-        <v>74.1624720357942</v>
+        <v>78.73601789709173</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I3" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -4171,39 +7207,55 @@
         <v>0</v>
       </c>
       <c r="M3" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.4173315412662693</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.156005425573318</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09189295975639943</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3796898464672829</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.4173315412662693</v>
-      </c>
+        <v>3.522415383945315</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>0.3610559870062211</v>
+        <v>3.853739961276858</v>
       </c>
       <c r="E4" s="4">
-        <v>83.54591836734694</v>
+        <v>80.13605442176872</v>
       </c>
       <c r="F4" s="4">
-        <v>78.73601789709173</v>
+        <v>74.1624720357942</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -4212,12 +7264,26 @@
         <v>0</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>3</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>3.522415383945315</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.3600521145166015</v>
@@ -4255,9 +7321,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.3169418593171096</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1362262994953755</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1362262994953755</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7352,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7371,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7413,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,25 +7444,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.08489111065753718</v>
+        <v>0.06298808781435739</v>
       </c>
       <c r="C3" s="4">
-        <v>0.07873249739448543</v>
+        <v>0.04832953112957788</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1239797510195615</v>
+        <v>0.07065999699214487</v>
       </c>
       <c r="E3" s="4">
-        <v>84.73214285714286</v>
+        <v>86.7389455782313</v>
       </c>
       <c r="F3" s="4">
-        <v>82.49720357941834</v>
+        <v>86.97706935123043</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
@@ -4386,25 +7503,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.04832953112957788</v>
+      </c>
+      <c r="O3" s="5">
+        <v>7</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.05739475460450347</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.03503293158551941</v>
+      </c>
+      <c r="R3" s="5">
+        <v>7</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.06298808781435739</v>
+        <v>0.08489111065753718</v>
       </c>
       <c r="C4" s="4">
-        <v>0.04832953112957788</v>
+        <v>0.07873249739448543</v>
       </c>
       <c r="D4" s="4">
-        <v>0.07065999699214487</v>
+        <v>0.1239797510195615</v>
       </c>
       <c r="E4" s="4">
-        <v>86.7389455782313</v>
+        <v>84.73214285714286</v>
       </c>
       <c r="F4" s="4">
-        <v>86.97706935123043</v>
+        <v>82.49720357941834</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
@@ -4427,10 +7562,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.03717306928478235</v>
+      </c>
+      <c r="O4" s="5">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.08244889164523528</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.07063095148260005</v>
+      </c>
+      <c r="R4" s="5">
+        <v>7</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.1155647104771366</v>
@@ -4468,9 +7621,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.1155647104771366</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.08030308462508513</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.08030308462508513</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7652,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7671,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7713,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,34 +7744,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1962280455604528</v>
+        <v>0.07878879687011775</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3218059068023607</v>
+        <v>0.08360816952994046</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2313215576513699</v>
+        <v>0.09229495917969288</v>
       </c>
       <c r="E3" s="4">
-        <v>83.171768707483</v>
+        <v>84.72363945578232</v>
       </c>
       <c r="F3" s="4">
-        <v>78.67030201342281</v>
+        <v>83.91079418344519</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I3" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -4599,34 +7803,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.01755130846897097</v>
+      </c>
+      <c r="O3" s="5">
+        <v>7</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.07878879687011775</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08611549931122202</v>
+      </c>
+      <c r="R3" s="5">
+        <v>7</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.07878879687011775</v>
+        <v>0.1962280455604528</v>
       </c>
       <c r="C4" s="4">
-        <v>0.08360816952994046</v>
+        <v>0.3218059068023607</v>
       </c>
       <c r="D4" s="4">
-        <v>0.09229495917969288</v>
+        <v>0.2313215576513699</v>
       </c>
       <c r="E4" s="4">
-        <v>84.72363945578232</v>
+        <v>83.171768707483</v>
       </c>
       <c r="F4" s="4">
-        <v>83.91079418344519</v>
+        <v>78.67030201342281</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -4640,10 +7862,26 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1962280455604528</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3218059068023607</v>
+      </c>
+      <c r="R4" s="5">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.1548822324234444</v>
@@ -4681,9 +7919,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1268892137700602</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1088291918925427</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1088291918925427</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7950,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7969,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8011,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,34 +8042,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1446739386800999</v>
+        <v>0.04999449086396268</v>
       </c>
       <c r="C3" s="4">
-        <v>0.04176866805882469</v>
+        <v>0.04999449086396268</v>
       </c>
       <c r="D3" s="4">
-        <v>0.06457708800475359</v>
+        <v>0.05249121022431424</v>
       </c>
       <c r="E3" s="4">
-        <v>93.44812925170066</v>
+        <v>95.90561224489795</v>
       </c>
       <c r="F3" s="4">
-        <v>87.14625279642058</v>
+        <v>95.92281879194631</v>
       </c>
       <c r="G3" s="5">
         <v>8</v>
       </c>
       <c r="H3" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -4812,34 +8101,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.02696670797729794</v>
+      </c>
+      <c r="O3" s="5">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.04820503807617271</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04820503807617271</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.04999449086396268</v>
+        <v>0.1446739386800999</v>
       </c>
       <c r="C4" s="4">
-        <v>0.04999449086396268</v>
+        <v>0.04176866805882469</v>
       </c>
       <c r="D4" s="4">
-        <v>0.05249121022431424</v>
+        <v>0.06457708800475359</v>
       </c>
       <c r="E4" s="4">
-        <v>95.90561224489795</v>
+        <v>93.44812925170066</v>
       </c>
       <c r="F4" s="4">
-        <v>95.92281879194631</v>
+        <v>87.14625279642058</v>
       </c>
       <c r="G4" s="5">
         <v>8</v>
       </c>
       <c r="H4" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -4853,10 +8160,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.04167156830639555</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1403470174492042</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.02651128042811252</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.0584759402995912</v>
@@ -4894,9 +8219,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.001251818728730671</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.05865477154655271</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.05865477154655271</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8250,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.2210586321204127</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.277614569047261</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.3718663839676637</v>
-      </c>
-      <c r="E3" s="4">
-        <v>85.57397959183673</v>
-      </c>
-      <c r="F3" s="4">
-        <v>68.29697986577182</v>
-      </c>
-      <c r="G3" s="5">
-        <v>8</v>
-      </c>
-      <c r="H3" s="5">
-        <v>5</v>
-      </c>
-      <c r="I3" s="5">
-        <v>3</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.1133061217779714</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1133061217779714</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.1124558214202782</v>
-      </c>
-      <c r="E4" s="4">
-        <v>91.27551020408163</v>
-      </c>
-      <c r="F4" s="4">
-        <v>89.23238255033557</v>
-      </c>
-      <c r="G4" s="5">
-        <v>8</v>
-      </c>
-      <c r="H4" s="5">
-        <v>8</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.09652670285565586</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.09652670285565586</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.09756500522856067</v>
-      </c>
-      <c r="E5" s="4">
-        <v>92.52186588921282</v>
-      </c>
-      <c r="F5" s="4">
-        <v>93.17833173537873</v>
-      </c>
-      <c r="G5" s="5">
-        <v>7</v>
-      </c>
-      <c r="H5" s="5">
-        <v>7</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.7164587818487576</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.9775003003887974</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.7760624729498318</v>
-      </c>
-      <c r="E3" s="4">
-        <v>79.93622448979592</v>
-      </c>
-      <c r="F3" s="4">
-        <v>69.04082774049216</v>
-      </c>
-      <c r="G3" s="5">
-        <v>8</v>
-      </c>
-      <c r="H3" s="5">
-        <v>4</v>
-      </c>
-      <c r="I3" s="5">
-        <v>2</v>
-      </c>
-      <c r="J3" s="5">
-        <v>2</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.5640655586395233</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.6545561948439484</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.5334202985279823</v>
-      </c>
-      <c r="E4" s="4">
-        <v>83.35884353741496</v>
-      </c>
-      <c r="F4" s="4">
-        <v>79.88394854586129</v>
-      </c>
-      <c r="G4" s="5">
-        <v>8</v>
-      </c>
-      <c r="H4" s="5">
-        <v>6</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>2</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>2</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.9567131164451439</v>
-      </c>
-      <c r="C5" s="4">
-        <v>1.075180016346928</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.9084772231956322</v>
-      </c>
-      <c r="E5" s="4">
-        <v>83.97473275024298</v>
-      </c>
-      <c r="F5" s="4">
-        <v>83.9181847235543</v>
-      </c>
-      <c r="G5" s="5">
-        <v>7</v>
-      </c>
-      <c r="H5" s="5">
-        <v>5</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>2</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>2</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/LeeEpitaxial2020.xlsx
+++ b/public/downloads/LeeEpitaxial2020.xlsx
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1133061217779714</v>
+        <v>0.06765136886278356</v>
       </c>
       <c r="O3" s="5">
         <v>8</v>
       </c>
       <c r="P3" s="4">
-        <v>0.08884565751940166</v>
+        <v>0.07118783484697344</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08884565751940166</v>
+        <v>0.07118783484697344</v>
       </c>
       <c r="R3" s="5">
         <v>8</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.277614569047261</v>
+        <v>0.2765286976713703</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1655839161310514</v>
+        <v>0.1650409804431061</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1744447667267249</v>
+        <v>0.1742275924515468</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -1675,16 +1675,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.09014831679262818</v>
+        <v>0.04551609662834188</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.0879551491263659</v>
+        <v>0.08157911767432502</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.0879551491263659</v>
+        <v>0.08157911767432502</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -1857,13 +1857,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.6545561948439484</v>
+        <v>0.6306226805926372</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1875474920198457</v>
+        <v>0.1815641134570178</v>
       </c>
       <c r="Q3" s="4">
         <v>0.1294091410872274</v>
@@ -1973,16 +1973,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>1.075180016346928</v>
+        <v>1.145599862823474</v>
       </c>
       <c r="O5" s="5">
         <v>5</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1980335990133864</v>
+        <v>0.2080935770814644</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1113933787562428</v>
+        <v>0.09730940946093369</v>
       </c>
       <c r="R5" s="5">
         <v>5</v>
@@ -2155,16 +2155,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.02296198970657626</v>
+        <v>-0.004927972379113577</v>
       </c>
       <c r="O3" s="5">
         <v>8</v>
       </c>
       <c r="P3" s="4">
-        <v>0.06981223397788872</v>
+        <v>0.06588244770069673</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06981223397788872</v>
+        <v>0.06588244770069673</v>
       </c>
       <c r="R3" s="5">
         <v>8</v>
@@ -2214,13 +2214,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.05394071196694365</v>
+        <v>0.08338926620652387</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.196863689653776</v>
+        <v>0.2042258282136711</v>
       </c>
       <c r="Q4" s="4">
         <v>0.08900115728393132</v>
@@ -2273,16 +2273,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.009238960732738428</v>
+        <v>0.1039875540348767</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1276093993440639</v>
+        <v>0.114073886015187</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1276093993440639</v>
+        <v>0.114073886015187</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -2455,7 +2455,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.04971069208705054</v>
+        <v>0.1000371842578147</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
@@ -2464,7 +2464,7 @@
         <v>0.1419359731494048</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1267679198469281</v>
+        <v>0.1195784209653904</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -2571,16 +2571,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1045510958980945</v>
+        <v>0.171118253420417</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1848499415991613</v>
+        <v>0.1753403476674009</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1848499415991613</v>
+        <v>0.1753403476674009</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.009904043945315522</v>
+        <v>-0.007915672353504988</v>
       </c>
       <c r="O3" s="5">
         <v>8</v>
@@ -2812,16 +2812,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.06429992150146784</v>
+        <v>-0.02252842982177583</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2059839314013701</v>
+        <v>0.2076953266308585</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09290109631511555</v>
+        <v>0.08125912606120285</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
@@ -2871,16 +2871,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.09128848341902085</v>
+        <v>0.1034326760864133</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.09438151545917403</v>
+        <v>0.09264663079240368</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.09438151545917403</v>
+        <v>0.09264663079240368</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -3053,16 +3053,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1397295112876731</v>
+        <v>-0.1515945524975564</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.06128644960453299</v>
+        <v>0.05832018930206218</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06095449657385991</v>
+        <v>0.05925949068673374</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -3112,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.09216840204589971</v>
+        <v>-0.06976131551266462</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
@@ -3121,7 +3121,7 @@
         <v>0.1789434498339872</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.07185559852540564</v>
+        <v>0.06737418121875863</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -3171,16 +3171,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.04044401843576192</v>
+        <v>0.04946747948486063</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.06778286653379419</v>
+        <v>0.06649380066963724</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.06778286653379419</v>
+        <v>0.06649380066963724</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -3353,16 +3353,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3116706846044168</v>
+        <v>0.2784464749864206</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1019887068809164</v>
+        <v>0.09368265447641733</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.09987371156104298</v>
+        <v>0.09512739590132924</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -3412,16 +3412,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.414034962318495</v>
+        <v>0.3606100330721347</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1366838403186976</v>
+        <v>0.1233276080071075</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1225702609533232</v>
+        <v>0.1149381282038432</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -3471,16 +3471,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3970233860392121</v>
+        <v>0.4111149816604858</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.08816369487721383</v>
+        <v>0.08444446439042556</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.08816369487721383</v>
+        <v>0.08444446439042556</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -3653,7 +3653,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3724018482197771</v>
+        <v>-0.3573528486024564</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
@@ -3662,7 +3662,7 @@
         <v>0.06231252140973265</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.05237709832422967</v>
+        <v>0.05022724123604101</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -3712,16 +3712,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4960441890446035</v>
+        <v>-0.4855012595500057</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.163136264403132</v>
+        <v>0.163415409102182</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.03944726496105962</v>
+        <v>0.03630514806159368</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
@@ -3771,16 +3771,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2177593262499791</v>
+        <v>-0.2026193387333954</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.03709456610906362</v>
+        <v>0.03493171074955167</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.03709456610906362</v>
+        <v>0.03493171074955167</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -3953,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.583208133809886</v>
+        <v>0.6338254011842821</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
@@ -3962,7 +3962,7 @@
         <v>0.1477209723504735</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08681526454016449</v>
+        <v>0.07669181106528526</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -4249,7 +4249,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2437350696052203</v>
+        <v>-0.2335101035153837</v>
       </c>
       <c r="O3" s="5">
         <v>8</v>
@@ -4308,16 +4308,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2406614878749153</v>
+        <v>-0.2509089436265697</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1846815729295457</v>
+        <v>0.1795578450537185</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.03983393486916952</v>
+        <v>0.03778444371883864</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -4367,16 +4367,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1804262635331309</v>
+        <v>-0.1831177861594391</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.02919788030050202</v>
+        <v>0.02881337706817228</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.02919788030050202</v>
+        <v>0.02881337706817228</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -4563,13 +4563,13 @@
         <v>13.04347826086956</v>
       </c>
       <c r="H4" s="4">
-        <v>1.320910894461595</v>
+        <v>1.309904160301671</v>
       </c>
       <c r="I4" s="4">
-        <v>0.1157647580773866</v>
+        <v>0.1022049060111145</v>
       </c>
       <c r="J4" s="4">
-        <v>1.459403975386669</v>
+        <v>1.459791150793885</v>
       </c>
       <c r="K4" s="4">
         <v>83.17805383022774</v>
@@ -4613,13 +4613,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.07308133749450024</v>
+        <v>0.06913418035179451</v>
       </c>
       <c r="I5" s="4">
-        <v>0.0619889892310682</v>
+        <v>0.05757185571294783</v>
       </c>
       <c r="J5" s="4">
-        <v>0.09028343932449844</v>
+        <v>0.09194008302520235</v>
       </c>
       <c r="K5" s="4">
         <v>86.40343093759242</v>
@@ -4663,13 +4663,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.1287799601170593</v>
+        <v>0.1277085722227953</v>
       </c>
       <c r="I6" s="4">
-        <v>0.1473242480908775</v>
+        <v>0.1441357360754394</v>
       </c>
       <c r="J6" s="4">
-        <v>0.1403086136101213</v>
+        <v>0.1449331030566947</v>
       </c>
       <c r="K6" s="4">
         <v>84.42324755989354</v>
@@ -4713,13 +4713,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.08343477587082107</v>
+        <v>0.08209747057234573</v>
       </c>
       <c r="I7" s="4">
-        <v>0.04643900537879067</v>
+        <v>0.04505694368554316</v>
       </c>
       <c r="J7" s="4">
-        <v>0.05415745624514322</v>
+        <v>0.05396159039231856</v>
       </c>
       <c r="K7" s="4">
         <v>95.10795622596865</v>
@@ -4763,13 +4763,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.1152662014386168</v>
+        <v>0.1069949715669962</v>
       </c>
       <c r="I8" s="4">
-        <v>0.10993375688367</v>
+        <v>0.1005847232376898</v>
       </c>
       <c r="J8" s="4">
-        <v>0.1146092535360559</v>
+        <v>0.112403575528413</v>
       </c>
       <c r="K8" s="4">
         <v>89.67169476486248</v>
@@ -4813,13 +4813,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.3747080601757622</v>
+        <v>0.3756886174789763</v>
       </c>
       <c r="I9" s="4">
-        <v>0.3495615294573178</v>
+        <v>0.3448668730255482</v>
       </c>
       <c r="J9" s="4">
-        <v>0.4266194208994908</v>
+        <v>0.4316422679614208</v>
       </c>
       <c r="K9" s="4">
         <v>82.35581188997338</v>
@@ -4863,13 +4863,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.1315944862809463</v>
+        <v>0.1286688438878805</v>
       </c>
       <c r="I10" s="4">
-        <v>0.09456050528262595</v>
+        <v>0.08855160606740337</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1225857052938357</v>
+        <v>0.118752473642524</v>
       </c>
       <c r="K10" s="4">
         <v>91.95652173913047</v>
@@ -4913,13 +4913,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.1948271868126995</v>
+        <v>0.1919329625725986</v>
       </c>
       <c r="I11" s="4">
-        <v>0.1849642358356063</v>
+        <v>0.1776583827297884</v>
       </c>
       <c r="J11" s="4">
-        <v>0.2058733502194809</v>
+        <v>0.1945285662458564</v>
       </c>
       <c r="K11" s="4">
         <v>89.12747707778766</v>
@@ -4963,13 +4963,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.1332449169926717</v>
+        <v>0.1333121765217376</v>
       </c>
       <c r="I12" s="4">
-        <v>0.09400801035767536</v>
+        <v>0.09010343825334828</v>
       </c>
       <c r="J12" s="4">
-        <v>0.107270426953808</v>
+        <v>0.111254066627355</v>
       </c>
       <c r="K12" s="4">
         <v>93.02573203194322</v>
@@ -5013,13 +5013,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.1041877939671618</v>
+        <v>0.1027637268598198</v>
       </c>
       <c r="I13" s="4">
-        <v>0.0663389228621372</v>
+        <v>0.06406020766254683</v>
       </c>
       <c r="J13" s="4">
-        <v>0.08255883270578172</v>
+        <v>0.08593134212036153</v>
       </c>
       <c r="K13" s="4">
         <v>89.22360248447202</v>
@@ -5063,13 +5063,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.1098489670320612</v>
+        <v>0.1011823195913556</v>
       </c>
       <c r="I14" s="4">
-        <v>0.1035358891305267</v>
+        <v>0.09816999616519932</v>
       </c>
       <c r="J14" s="4">
-        <v>0.08599419481454855</v>
+        <v>0.08988979090835005</v>
       </c>
       <c r="K14" s="4">
         <v>80.89322685595977</v>
@@ -5113,13 +5113,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.08970661953332011</v>
+        <v>0.08914545301487733</v>
       </c>
       <c r="I15" s="4">
-        <v>0.04314926203997053</v>
+        <v>0.04069717761343554</v>
       </c>
       <c r="J15" s="4">
-        <v>0.05268319714153057</v>
+        <v>0.05314117581719434</v>
       </c>
       <c r="K15" s="4">
         <v>96.35314995563444</v>
@@ -5166,7 +5166,7 @@
         <v>0.4387919506086683</v>
       </c>
       <c r="I16" s="4">
-        <v>0.4187375798977445</v>
+        <v>0.4148439439458679</v>
       </c>
       <c r="J16" s="4">
         <v>0.4724892259282846</v>
@@ -5213,13 +5213,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.09175420651275559</v>
+        <v>0.08985501757219361</v>
       </c>
       <c r="I17" s="4">
-        <v>0.04160319203514303</v>
+        <v>0.04095624311624491</v>
       </c>
       <c r="J17" s="4">
-        <v>0.05198712800386202</v>
+        <v>0.05008989468606682</v>
       </c>
       <c r="K17" s="4">
         <v>94.99112688553681</v>
@@ -7210,16 +7210,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.4173315412662693</v>
+        <v>0.3788931368579114</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.156005425573318</v>
+        <v>0.1403872163714581</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.09189295975639943</v>
+        <v>0.08388148229003889</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -7322,16 +7322,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3169418593171096</v>
+        <v>0.3756237237548703</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1362262994953755</v>
+        <v>0.1179106977720364</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1362262994953755</v>
+        <v>0.1179106977720364</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -7504,16 +7504,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.04832953112957788</v>
+        <v>0.0329524520205382</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.05739475460450347</v>
+        <v>0.05140896913567516</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.03503293158551941</v>
+        <v>0.03038875949386417</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -7563,7 +7563,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.03717306928478235</v>
+        <v>-0.05452533799211778</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
@@ -7572,7 +7572,7 @@
         <v>0.08244889164523528</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.07063095148260005</v>
+        <v>0.06815205595298071</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -7622,16 +7622,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1155647104771366</v>
+        <v>-0.07266637994553093</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.08030308462508513</v>
+        <v>0.07417475169199861</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.08030308462508513</v>
+        <v>0.07417475169199861</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -7804,7 +7804,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.01755130846897097</v>
+        <v>-0.01519998624084451</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
@@ -7813,7 +7813,7 @@
         <v>0.07878879687011775</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08611549931122202</v>
+        <v>0.08143674292410553</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -7920,16 +7920,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1268892137700602</v>
+        <v>0.1515311353381321</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1088291918925427</v>
+        <v>0.1053089173828182</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1088291918925427</v>
+        <v>0.1053089173828182</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -8102,7 +8102,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.02696670797729794</v>
+        <v>-0.01910165169800848</v>
       </c>
       <c r="O3" s="5">
         <v>8</v>
@@ -8161,16 +8161,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.04167156830639555</v>
+        <v>0.03855478030641279</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1403470174492042</v>
+        <v>0.1395678204492086</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.02651128042811252</v>
+        <v>0.02588792282811596</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -8220,16 +8220,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.001251818728730671</v>
+        <v>-0.02327262713623668</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.05865477154655271</v>
+        <v>0.05515127928012881</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.05865477154655271</v>
+        <v>0.05515127928012881</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
